--- a/InputData/elec/BDPbES/BAU Dispatch Priority by Elec Source.xlsx
+++ b/InputData/elec/BDPbES/BAU Dispatch Priority by Elec Source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\IA\elec\BDPbES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\elec\BDPbES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{440F540A-03CB-437F-BF34-F1FF2232E923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05002382-202A-4BFB-9F71-B62C33F79EA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -34,13 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
-  <si>
-    <t>BDPbES BAU Dispatch Priority by Electricity Source</t>
-  </si>
-  <si>
-    <t>Iowa</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Notes:</t>
   </si>
@@ -48,34 +42,10 @@
     <t>This variable is used to specify the priority ordering of the different electricity sources</t>
   </si>
   <si>
-    <t>for purposes of guaranteed dispatch.</t>
-  </si>
-  <si>
-    <t>We assign priority 1 to natural gas peaker and petroleum-fired plants, which are the</t>
-  </si>
-  <si>
-    <t>only types for which a non-zero quantity is specified for guaranteed dispatch in the BAU case</t>
-  </si>
-  <si>
-    <t>for the United States.  We arbitrarily assign priority 2 to all other plant types.</t>
-  </si>
-  <si>
-    <t>Priority Order (dimensionless)</t>
-  </si>
-  <si>
-    <t>hard coal</t>
-  </si>
-  <si>
-    <t>natural gas nonpeaker</t>
-  </si>
-  <si>
     <t>nuclear</t>
   </si>
   <si>
     <t>hydro</t>
-  </si>
-  <si>
-    <t>onshore wind</t>
   </si>
   <si>
     <t>solar PV</t>
@@ -87,6 +57,12 @@
     <t>biomass</t>
   </si>
   <si>
+    <t>BDPbES BAU Dispatch Priority by Electricity Source</t>
+  </si>
+  <si>
+    <t>natural gas nonpeaker</t>
+  </si>
+  <si>
     <t>geothermal</t>
   </si>
   <si>
@@ -96,7 +72,25 @@
     <t>natural gas peaker</t>
   </si>
   <si>
+    <t>for purposes of guaranteed dispatch.</t>
+  </si>
+  <si>
+    <t>We assign priority 1 to natural gas peaker and petroleum-fired plants, which are the</t>
+  </si>
+  <si>
+    <t>for the United States.  We arbitrarily assign priority 2 to all other plant types.</t>
+  </si>
+  <si>
+    <t>only types for which a non-zero quantity is specified for guaranteed dispatch in the BAU case</t>
+  </si>
+  <si>
     <t>lignite</t>
+  </si>
+  <si>
+    <t>hard coal</t>
+  </si>
+  <si>
+    <t>onshore wind</t>
   </si>
   <si>
     <t>offshore wind</t>
@@ -109,6 +103,9 @@
   </si>
   <si>
     <t>municipal solid waste</t>
+  </si>
+  <si>
+    <t>Priority Order (dimensionless)</t>
   </si>
   <si>
     <t>hard coal w CCS</t>
@@ -496,50 +493,47 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>4</v>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>5</v>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -555,9 +549,9 @@
     <col min="2" max="2" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B1" s="2">
         <v>2015</v>
@@ -670,17 +664,17 @@
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B2">
         <v>2</v>
       </c>
       <c r="C2">
-        <f t="shared" ref="C2:L11" si="0">$B2</f>
+        <f>$B2</f>
         <v>2</v>
       </c>
       <c r="D2">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D2:AK9" si="0">$B2</f>
         <v>2</v>
       </c>
       <c r="E2">
@@ -716,151 +710,151 @@
         <v>2</v>
       </c>
       <c r="M2">
-        <f t="shared" ref="M2:V11" si="1">$B2</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="N2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="O2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="P2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="Q2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="R2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="S2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="T2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="U2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="V2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="W2">
-        <f t="shared" ref="W2:AK11" si="2">$B2</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="X2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="Y2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="Z2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AA2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AB2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AC2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AD2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AE2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AF2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AG2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AH2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AI2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AJ2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AK2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="C3:R12" si="1">$B3</f>
         <v>2</v>
       </c>
       <c r="D3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="E3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="F3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="G3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="H3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="I3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="J3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="K3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="L3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="M3">
@@ -888,91 +882,91 @@
         <v>2</v>
       </c>
       <c r="S3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="T3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="U3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="V3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="W3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="X3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="Y3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="Z3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AA3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AB3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AC3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AD3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AE3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AF3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AG3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AH3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AI3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AJ3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AK3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
       <c r="C4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="D4">
@@ -1012,115 +1006,115 @@
         <v>2</v>
       </c>
       <c r="M4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="N4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="O4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="P4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="Q4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="R4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="S4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="T4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="U4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="V4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="W4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="X4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="Y4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="Z4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AA4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AB4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AC4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AD4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AE4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AF4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AG4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AH4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AI4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AJ4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AK4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="D5">
@@ -1160,115 +1154,115 @@
         <v>2</v>
       </c>
       <c r="M5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="N5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="O5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="P5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="Q5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="R5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="S5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="T5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="U5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="V5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="W5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="X5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="Y5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="Z5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AA5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AB5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AC5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AD5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AE5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AF5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AG5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AH5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AI5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AJ5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AK5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="D6">
@@ -1308,115 +1302,115 @@
         <v>2</v>
       </c>
       <c r="M6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="N6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="O6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="P6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="Q6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="R6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="S6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="T6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="U6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="V6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="W6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="X6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="Y6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="Z6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AA6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AB6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AC6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AD6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AE6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AF6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AG6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AH6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AI6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AJ6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AK6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="D7">
@@ -1456,115 +1450,115 @@
         <v>2</v>
       </c>
       <c r="M7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="N7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="O7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="P7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="Q7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="R7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="S7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="T7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="U7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="V7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="W7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="X7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="Y7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="Z7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AA7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AB7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AC7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AD7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AE7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AF7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AG7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AH7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AI7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AJ7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AK7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
       <c r="C8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="D8">
@@ -1604,115 +1598,115 @@
         <v>2</v>
       </c>
       <c r="M8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="N8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="O8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="P8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="Q8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="R8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="S8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="T8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="U8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="V8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="W8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="X8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="Y8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="Z8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AA8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AB8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AC8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AD8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AE8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AF8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AG8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AH8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AI8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AJ8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AK8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="D9">
@@ -1752,99 +1746,99 @@
         <v>2</v>
       </c>
       <c r="M9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="N9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="O9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="P9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="Q9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="R9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="S9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="T9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="U9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="V9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="W9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="X9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="Y9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="Z9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AA9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AB9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AC9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AD9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AE9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AF9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AG9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AH9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AI9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="AJ9">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="D9:AK17" si="2">$B9</f>
         <v>2</v>
       </c>
       <c r="AK9">
@@ -1854,89 +1848,89 @@
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="D10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="E10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="F10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="G10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="I10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="J10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="K10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="L10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="M10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="N10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="O10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="P10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="Q10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="R10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="S10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="T10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="U10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="V10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="W10">
@@ -2002,89 +1996,89 @@
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="D11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="I11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="J11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="K11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="L11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="P11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="T11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="U11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="V11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="W11">
@@ -2150,599 +2144,599 @@
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12">
-        <f t="shared" ref="C12:L24" si="3">$B12</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="D12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="I12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="J12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="K12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="L12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M12">
-        <f t="shared" ref="M12:V24" si="4">$B12</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="P12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="T12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="U12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="V12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="W12">
-        <f t="shared" ref="W12:AK24" si="5">$B12</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="X12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="Y12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="Z12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AA12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AB12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AC12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AD12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AE12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AG12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AH12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AI12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AJ12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AK12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13">
-        <f t="shared" si="3"/>
+        <f>$B13</f>
         <v>2</v>
       </c>
       <c r="D13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="E13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="F13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="G13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="I13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="J13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="K13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="L13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="M13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="N13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="O13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="P13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="Q13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="R13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="S13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="T13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="U13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="V13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="W13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="X13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="Y13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="Z13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AA13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AB13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AC13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AD13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AE13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AF13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AG13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AH13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AI13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AJ13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AK13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14">
-        <f t="shared" si="3"/>
+        <f>$B14</f>
         <v>2</v>
       </c>
       <c r="D14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="E14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="F14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="G14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="I14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="J14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="K14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="L14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="M14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="N14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="O14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="P14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="R14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="S14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="T14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="U14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="V14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="W14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="X14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="Y14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="Z14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AA14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AB14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AC14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AD14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AE14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AF14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AG14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AH14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AI14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AJ14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AK14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="C15:R24" si="3">$B15</f>
         <v>2</v>
       </c>
       <c r="D15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="E15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="F15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="G15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="I15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="J15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="K15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="L15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="M15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="N15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="O15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="P15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="Q15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="R15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="S15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="T15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="U15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="V15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="W15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="X15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="Y15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="Z15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AA15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AB15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AC15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AD15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AE15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AF15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AG15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AH15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AI15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AJ15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AK15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B16">
         <v>2</v>
@@ -2752,145 +2746,145 @@
         <v>2</v>
       </c>
       <c r="D16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="E16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="F16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="G16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="I16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="J16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="K16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="L16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="M16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="N16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="O16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="P16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="Q16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="R16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="S16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="T16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="U16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="V16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="W16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="X16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="Y16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="Z16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AA16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AB16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AC16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AD16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AE16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AF16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AG16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AH16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AI16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AJ16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AK16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B17">
         <v>2</v>
@@ -2900,67 +2894,67 @@
         <v>2</v>
       </c>
       <c r="D17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="E17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="F17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="G17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="I17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="J17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="K17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="L17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="M17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="N17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="O17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="P17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="Q17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="R17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="S17">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="S17:AK18" si="4">$B17</f>
         <v>2</v>
       </c>
       <c r="T17">
@@ -2976,69 +2970,69 @@
         <v>2</v>
       </c>
       <c r="W17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="X17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="Y17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="Z17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="AA17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="AB17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="AC17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="AD17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="AE17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="AF17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="AG17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="AH17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="AI17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="AJ17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="AK17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18">
         <v>2</v>
@@ -3084,27 +3078,27 @@
         <v>2</v>
       </c>
       <c r="M18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="N18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="O18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="P18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="Q18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="R18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="S18">
@@ -3124,69 +3118,69 @@
         <v>2</v>
       </c>
       <c r="W18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="X18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="Y18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="Z18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="AA18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="AB18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="AC18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="AD18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="AE18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="AF18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="AG18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="AH18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="AI18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="AJ18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="AK18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19">
         <v>2</v>
@@ -3196,79 +3190,79 @@
         <v>2</v>
       </c>
       <c r="D19">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="D19:AK24" si="5">$B19</f>
         <v>2</v>
       </c>
       <c r="E19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="F19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="G19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="I19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="J19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="K19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="L19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="M19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="N19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="O19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="P19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="Q19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="R19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="S19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="T19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="U19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="V19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="W19">
@@ -3334,7 +3328,7 @@
     </row>
     <row r="20" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20">
         <v>2</v>
@@ -3344,79 +3338,79 @@
         <v>2</v>
       </c>
       <c r="D20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="E20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="F20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="G20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="I20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="J20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="K20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="L20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="M20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="N20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="O20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="P20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="Q20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="R20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="S20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="T20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="U20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="V20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="W20">
@@ -3482,7 +3476,7 @@
     </row>
     <row r="21" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21">
         <v>2</v>
@@ -3492,79 +3486,79 @@
         <v>2</v>
       </c>
       <c r="D21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="E21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="F21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="G21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="I21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="J21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="K21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="L21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="M21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="N21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="O21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="P21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="Q21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="R21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="S21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="T21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="U21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="V21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="W21">
@@ -3630,7 +3624,7 @@
     </row>
     <row r="22" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22">
         <v>2</v>
@@ -3640,79 +3634,79 @@
         <v>2</v>
       </c>
       <c r="D22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="E22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="F22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="G22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="I22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="J22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="K22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="L22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="M22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="N22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="O22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="P22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="Q22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="R22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="S22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="T22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="U22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="V22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="W22">
@@ -3778,7 +3772,7 @@
     </row>
     <row r="23" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23">
         <v>2</v>
@@ -3788,79 +3782,79 @@
         <v>2</v>
       </c>
       <c r="D23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="E23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="F23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="G23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="I23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="J23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="K23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="L23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="M23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="N23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="O23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="P23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="Q23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="R23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="S23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="T23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="U23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="V23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="W23">
@@ -3926,7 +3920,7 @@
     </row>
     <row r="24" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24">
         <v>2</v>
@@ -3936,79 +3930,79 @@
         <v>2</v>
       </c>
       <c r="D24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="E24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="F24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="G24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="I24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="J24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="K24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="L24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="M24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="N24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="O24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="P24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="Q24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="R24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="S24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="T24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="U24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="V24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="W24">
